--- a/teams-template.xlsx
+++ b/teams-template.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teams" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,9 +25,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -45,7 +51,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -53,18 +59,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,542 +454,626 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>MemberEmail</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>SecurityGroupNameExample</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>team1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>member1.team1@contoso.com</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team1</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>team01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>team01_person1@company.com</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>team1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>member2.team1@contoso.com</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team1</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>team01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>team01_person2@company.com</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>team1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>member3.team1@contoso.com</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team1</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>team01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>team01_person3@company.com</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>team1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>member4.team1@contoso.com</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team1</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>team01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>team01_person4@company.com</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>team1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>member5.team1@contoso.com</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team1</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>team01</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>team01_person5@company.com</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>team2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>member1.team2@contoso.com</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team2</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>team02</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>team02_person1@company.com</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>team2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>member2.team2@contoso.com</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team2</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>team02</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>team02_person2@company.com</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>team2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>member3.team2@contoso.com</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team2</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>team02</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>team02_person3@company.com</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>team2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>member4.team2@contoso.com</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team2</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>team02</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>team02_person4@company.com</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>team2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>member5.team2@contoso.com</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team2</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>team02</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>team02_person5@company.com</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>team3</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>member1.team3@contoso.com</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team3</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>team03</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>team03_person1@company.com</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>team3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>member2.team3@contoso.com</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team3</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>team03</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>team03_person2@company.com</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>team3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>member3.team3@contoso.com</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team3</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>team03</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>team03_person3@company.com</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>team3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>member4.team3@contoso.com</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team3</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>team03</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>team03_person4@company.com</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>team3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>member5.team3@contoso.com</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team3</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>team03</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>team03_person5@company.com</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>team4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>member1.team4@contoso.com</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team4</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>team04</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>team04_person1@company.com</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>team4</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>member2.team4@contoso.com</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team4</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>team04</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>team04_person2@company.com</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>team4</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>member3.team4@contoso.com</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team4</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>team04</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>team04_person3@company.com</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>team4</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>member4.team4@contoso.com</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team4</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>team04</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>team04_person4@company.com</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>team4</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>member5.team4@contoso.com</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team4</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>team04</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>team04_person5@company.com</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>team5</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>member1.team5@contoso.com</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team5</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>team05</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>team05_person1@company.com</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>team5</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>member2.team5@contoso.com</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team5</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>team05</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>team05_person2@company.com</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>team5</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>member3.team5@contoso.com</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team5</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>team05</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>team05_person3@company.com</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>team5</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>member4.team5@contoso.com</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team5</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>team05</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>team05_person4@company.com</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>team5</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>member5.team5@contoso.com</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team5</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>team05</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>team05_person5@company.com</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>team6</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>member1.team6@contoso.com</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team6</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>team06</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>team06_person1@company.com</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>team6</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>member2.team6@contoso.com</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team6</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>team06</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>team06_person2@company.com</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>team6</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>member3.team6@contoso.com</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team6</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>team06</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>team06_person3@company.com</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>team6</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>member4.team6@contoso.com</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team6</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>team06</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>team06_person4@company.com</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>team6</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>member5.team6@contoso.com</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>sg-bis-day-team6</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>team06</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>team06_person5@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>team07</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>team07_person1@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>team07</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>team07_person2@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>team07</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>team07_person3@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>team07</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>team07_person4@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>team07</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>team07_person5@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>team08</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>team08_person1@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>team08</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>team08_person2@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>team08</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>team08_person3@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>team08</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>team08_person4@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>team08</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>team08_person5@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>team09</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>team09_person1@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>team09</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>team09_person2@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>team09</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>team09_person3@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>team09</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>team09_person4@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>team09</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>team09_person5@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>team10</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>team10_person1@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>team10</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>team10_person2@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>team10</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>team10_person3@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>team10</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>team10_person4@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>team10</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>team10_person5@company.com</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>